--- a/uploads/Trail.xlsx
+++ b/uploads/Trail.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Harish S\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{213D3C66-C176-4DCE-ADA0-67EFE15223FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98900597-4D69-43AE-8E49-CCF2886D362B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11712" yWindow="0" windowWidth="11424" windowHeight="13056" xr2:uid="{677CC8E3-D787-44A1-92C9-B860CD4EE379}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{677CC8E3-D787-44A1-92C9-B860CD4EE379}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,75 +34,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>College Name</t>
   </si>
   <si>
-    <t>Event</t>
-  </si>
-  <si>
     <t>Name</t>
   </si>
   <si>
     <t>Ramco Institute of Technology</t>
   </si>
   <si>
-    <t>R. Sonali Priyadharshini</t>
-  </si>
-  <si>
-    <t>P. Vikneshwari</t>
-  </si>
-  <si>
-    <t>Jayasree S N</t>
-  </si>
-  <si>
-    <t>I. Geetha</t>
-  </si>
-  <si>
-    <t>S. Gayathiri</t>
-  </si>
-  <si>
-    <t>M. Keerthanalakshmi</t>
-  </si>
-  <si>
-    <t>S. Ramya</t>
-  </si>
-  <si>
-    <t>S. Priya dharshini</t>
-  </si>
-  <si>
-    <t>D. Priyadharshini</t>
-  </si>
-  <si>
-    <t>Anushree</t>
-  </si>
-  <si>
-    <t>S.A. Aashika</t>
-  </si>
-  <si>
-    <t>M.S. Prethipa</t>
-  </si>
-  <si>
-    <t>M. Uma Maheswari</t>
-  </si>
-  <si>
-    <t>M. Theetsetha</t>
-  </si>
-  <si>
-    <t>Food Frenzy</t>
-  </si>
-  <si>
-    <t>Pixel Craft 2050</t>
-  </si>
-  <si>
-    <t>Duo Leveling</t>
-  </si>
-  <si>
-    <t>Treasure Hunt</t>
-  </si>
-  <si>
-    <t>S. Vishaga</t>
+    <t>email</t>
+  </si>
+  <si>
+    <t>Keerthi</t>
+  </si>
+  <si>
+    <t>953623103015@ritrjpm.ac.in</t>
   </si>
 </sst>
 </file>
@@ -160,10 +109,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -481,208 +428,51 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A578FDA-1A96-477B-ABF7-DA94AA666CC8}">
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="41.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" s="2"/>
+        <v>5</v>
+      </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="2"/>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="1"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="2"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="2"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>21</v>
-      </c>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{1734EA8B-FB08-432B-9D65-D9CDA139FB95}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>